--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -452,10 +452,10 @@
         <v/>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>PF3Y9355</v>
       </c>
       <c r="F2" t="str">
         <v>Ajinkya</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="mm-dd-yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm\-dd\-yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -493,10 +493,10 @@
         <v/>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F3" t="str">
         <v>Kavita</v>
@@ -534,10 +534,10 @@
         <v/>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="F4" t="str">
         <v>Pradnya</v>
@@ -575,10 +575,10 @@
         <v/>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>HP</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F5" t="str">
         <v>Rachna Solanki</v>
@@ -616,10 +616,10 @@
         <v/>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>Dell</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>J9LDVF2</v>
       </c>
       <c r="F6" t="str">
         <v>Aarju Wasnik</v>
@@ -657,10 +657,10 @@
         <v/>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>HP</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>5CG10294SF</v>
       </c>
       <c r="F7" t="str">
         <v>Himanshu Tayde</v>
@@ -698,10 +698,10 @@
         <v/>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>Temp Laptop</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F8" t="str">
         <v xml:space="preserve">Preshita </v>
@@ -739,10 +739,10 @@
         <v/>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="F9" t="str">
         <v>Jivika</v>
@@ -780,10 +780,10 @@
         <v/>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F10" t="str">
         <v>Swapnali Patekar</v>
@@ -824,7 +824,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>HQRYDB3</v>
       </c>
       <c r="F11" t="str">
         <v>Abhishek mishra</v>
@@ -865,7 +865,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F12" t="str">
         <v>Sunny Ansul</v>
@@ -903,10 +903,10 @@
         <v/>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F13" t="str">
         <v>Palak Annawadiya</v>
@@ -944,10 +944,10 @@
         <v/>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F14" t="str">
         <v>Anusha Badole</v>
@@ -985,10 +985,10 @@
         <v/>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F15" t="str">
         <v>Disha Pangal</v>
@@ -1026,10 +1026,10 @@
         <v/>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F16" t="str">
         <v>Sakshi Ghorpade</v>
@@ -1067,10 +1067,10 @@
         <v/>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F17" t="str">
         <v>Suman Yadav</v>
@@ -1108,10 +1108,10 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>PRPL 293 HP LAPTOP</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F18" t="str">
         <v>Preshita Damahe</v>
@@ -1149,10 +1149,10 @@
         <v/>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>PF3P6ZDE</v>
       </c>
       <c r="F19" t="str">
         <v>Aman singh</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -531,13 +531,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D4" t="str">
-        <v>-</v>
+        <v>M17 5g</v>
       </c>
       <c r="E4" t="str">
-        <v>-</v>
+        <v>355242460501645</v>
       </c>
       <c r="F4" t="str">
         <v>Pradnya</v>
@@ -558,7 +558,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M4" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -470,7 +470,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K2" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -470,7 +470,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K2" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,25 +446,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>1</v>
+        <v>PRPL/LAP/1476</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D2" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 415 DELL LAPTOP</v>
       </c>
       <c r="E2" t="str">
-        <v>PF3Y9355</v>
+        <v>DK85RQ2</v>
       </c>
       <c r="F2" t="str">
-        <v>Ajinkya</v>
+        <v>Returned by Kanishka</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>PRPL / ACQ / 06042023 / 00216</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>Working</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L2" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -487,7 +487,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -496,10 +496,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E3" t="str">
-        <v>PF3Z9PCW</v>
+        <v>PF3Y9355</v>
       </c>
       <c r="F3" t="str">
-        <v>Kavita</v>
+        <v>Ajinkya</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -528,19 +528,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="str">
-        <v>Mobile</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>M17 5g</v>
+        <v>Lenovo</v>
       </c>
       <c r="E4" t="str">
-        <v>355242460501645</v>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F4" t="str">
-        <v>Pradnya</v>
+        <v>Kavita</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -558,7 +558,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>With cable</v>
+        <v>#N/A</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -569,19 +569,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D5" t="str">
-        <v>HP</v>
+        <v>M17 5g</v>
       </c>
       <c r="E5" t="str">
-        <v>5CG1223Y8W</v>
+        <v>355242460501645</v>
       </c>
       <c r="F5" t="str">
-        <v>Rachna Solanki</v>
+        <v>Pradnya</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -610,19 +610,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>Dell</v>
+        <v>HP</v>
       </c>
       <c r="E6" t="str">
-        <v>J9LDVF2</v>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F6" t="str">
-        <v>Aarju Wasnik</v>
+        <v>Rachna Solanki</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -651,19 +651,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>HP</v>
+        <v>Dell</v>
       </c>
       <c r="E7" t="str">
-        <v>5CG10294SF</v>
+        <v>J9LDVF2</v>
       </c>
       <c r="F7" t="str">
-        <v>Himanshu Tayde</v>
+        <v>Aarju Wasnik</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>Temp Laptop</v>
+        <v>HP</v>
       </c>
       <c r="E8" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG10294SF</v>
       </c>
       <c r="F8" t="str">
-        <v xml:space="preserve">Preshita </v>
+        <v>Himanshu Tayde</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -733,19 +733,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>Lenovo</v>
+        <v>Temp Laptop</v>
       </c>
       <c r="E9" t="str">
-        <v>-</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F9" t="str">
-        <v>Jivika</v>
+        <v xml:space="preserve">Preshita </v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -774,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -783,10 +783,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E10" t="str">
-        <v>PF37ZPG5</v>
+        <v>-</v>
       </c>
       <c r="F10" t="str">
-        <v>Swapnali Patekar</v>
+        <v>Jivika</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -815,19 +815,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E11" t="str">
-        <v>HQRYDB3</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F11" t="str">
-        <v>Abhishek mishra</v>
+        <v>Swapnali Patekar</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -865,10 +865,10 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>PF37ZPG5</v>
+        <v>HQRYDB3</v>
       </c>
       <c r="F12" t="str">
-        <v>Sunny Ansul</v>
+        <v>Abhishek mishra</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -897,19 +897,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>PRPL 14 HP LAPTOP</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>5CG0346B2F</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F13" t="str">
-        <v>Palak Annawadiya</v>
+        <v>Sunny Ansul</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -938,19 +938,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>PRPL 265 HP LAPTOP</v>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E14" t="str">
-        <v>5CG1223Y45</v>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F14" t="str">
-        <v>Anusha Badole</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -979,19 +979,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E15" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F15" t="str">
-        <v>Disha Pangal</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1020,19 +1020,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E16" t="str">
-        <v>PF37KGPZ</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F16" t="str">
-        <v>Sakshi Ghorpade</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1061,19 +1061,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>Lenovo</v>
       </c>
       <c r="E17" t="str">
-        <v>5CG1223Y30</v>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F17" t="str">
-        <v>Suman Yadav</v>
+        <v>Sakshi Ghorpade</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1102,19 +1102,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>PRPL 293 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E18" t="str">
-        <v>5CG1223Y8W</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F18" t="str">
-        <v>Preshita Damahe</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1143,45 +1143,86 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
+        <v>17</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>PRPL 293 HP LAPTOP</v>
+      </c>
+      <c r="E19" t="str">
+        <v>5CG1223Y8W</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Preshita Damahe</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
         <v>18</v>
       </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
         <v>Lenovo</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E20" t="str">
         <v>PF3P6ZDE</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F20" t="str">
         <v>Aman singh</v>
       </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
-        <v>Working</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v>#N/A</v>
-      </c>
-      <c r="M19" t="str">
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M20" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,25 +446,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>PRPL/LAP/1476</v>
+        <v>PRPL/MOB/3826</v>
       </c>
       <c r="C2" t="str">
-        <v>Purchased Laptop</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>PRPL 415 DELL LAPTOP</v>
+        <v>PRPL 273 SAMSUNG MOBILE</v>
       </c>
       <c r="E2" t="str">
-        <v>DK85RQ2</v>
+        <v>350284941590594</v>
       </c>
       <c r="F2" t="str">
-        <v>Returned by Kanishka</v>
+        <v>Returned by kanishka</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>PRPL / ACQ / 06042023 / 00216</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -476,7 +476,7 @@
         <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L2" t="str">
-        <v>24-10-26</v>
+        <v>24-10-2026</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -487,25 +487,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>1</v>
+        <v>PRPL/LAP/1476</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D3" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 415 DELL LAPTOP</v>
       </c>
       <c r="E3" t="str">
-        <v>PF3Y9355</v>
+        <v>DK85RQ2</v>
       </c>
       <c r="F3" t="str">
-        <v>Ajinkya</v>
+        <v>Returned by Kanishka</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>PRPL / ACQ / 06042023 / 00216</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -514,10 +514,10 @@
         <v>Working</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L3" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -528,7 +528,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -537,10 +537,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E4" t="str">
-        <v>PF3Z9PCW</v>
+        <v>PF3Y9355</v>
       </c>
       <c r="F4" t="str">
-        <v>Kavita</v>
+        <v>Ajinkya</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -569,19 +569,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="str">
-        <v>Mobile</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>M17 5g</v>
+        <v>Lenovo</v>
       </c>
       <c r="E5" t="str">
-        <v>355242460501645</v>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F5" t="str">
-        <v>Pradnya</v>
+        <v>Kavita</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>With cable</v>
+        <v>#N/A</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -610,19 +610,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D6" t="str">
-        <v>HP</v>
+        <v>M17 5g</v>
       </c>
       <c r="E6" t="str">
-        <v>5CG1223Y8W</v>
+        <v>355242460501645</v>
       </c>
       <c r="F6" t="str">
-        <v>Rachna Solanki</v>
+        <v>Pradnya</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -640,7 +640,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -651,19 +651,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>Dell</v>
+        <v>HP</v>
       </c>
       <c r="E7" t="str">
-        <v>J9LDVF2</v>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F7" t="str">
-        <v>Aarju Wasnik</v>
+        <v>Rachna Solanki</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>HP</v>
+        <v>Dell</v>
       </c>
       <c r="E8" t="str">
-        <v>5CG10294SF</v>
+        <v>J9LDVF2</v>
       </c>
       <c r="F8" t="str">
-        <v>Himanshu Tayde</v>
+        <v>Aarju Wasnik</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -733,19 +733,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>Temp Laptop</v>
+        <v>HP</v>
       </c>
       <c r="E9" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG10294SF</v>
       </c>
       <c r="F9" t="str">
-        <v xml:space="preserve">Preshita </v>
+        <v>Himanshu Tayde</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -774,19 +774,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>Lenovo</v>
+        <v>Temp Laptop</v>
       </c>
       <c r="E10" t="str">
-        <v>-</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F10" t="str">
-        <v>Jivika</v>
+        <v xml:space="preserve">Preshita </v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -815,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -824,10 +824,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E11" t="str">
-        <v>PF37ZPG5</v>
+        <v>-</v>
       </c>
       <c r="F11" t="str">
-        <v>Swapnali Patekar</v>
+        <v>Jivika</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -856,19 +856,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E12" t="str">
-        <v>HQRYDB3</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F12" t="str">
-        <v>Abhishek mishra</v>
+        <v>Swapnali Patekar</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -897,7 +897,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -906,10 +906,10 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>PF37ZPG5</v>
+        <v>HQRYDB3</v>
       </c>
       <c r="F13" t="str">
-        <v>Sunny Ansul</v>
+        <v>Abhishek mishra</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -938,19 +938,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>PRPL 14 HP LAPTOP</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>5CG0346B2F</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F14" t="str">
-        <v>Palak Annawadiya</v>
+        <v>Sunny Ansul</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -979,19 +979,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>PRPL 265 HP LAPTOP</v>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E15" t="str">
-        <v>5CG1223Y45</v>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F15" t="str">
-        <v>Anusha Badole</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1020,19 +1020,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E16" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F16" t="str">
-        <v>Disha Pangal</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1061,19 +1061,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E17" t="str">
-        <v>PF37KGPZ</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F17" t="str">
-        <v>Sakshi Ghorpade</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1102,19 +1102,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>Lenovo</v>
       </c>
       <c r="E18" t="str">
-        <v>5CG1223Y30</v>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F18" t="str">
-        <v>Suman Yadav</v>
+        <v>Sakshi Ghorpade</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1143,19 +1143,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>PRPL 293 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E19" t="str">
-        <v>5CG1223Y8W</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F19" t="str">
-        <v>Preshita Damahe</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1184,45 +1184,86 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
+        <v>17</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>PRPL 293 HP LAPTOP</v>
+      </c>
+      <c r="E20" t="str">
+        <v>5CG1223Y8W</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Preshita Damahe</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
         <v>18</v>
       </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
         <v>Lenovo</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E21" t="str">
         <v>PF3P6ZDE</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F21" t="str">
         <v>Aman singh</v>
       </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v>Working</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v>#N/A</v>
-      </c>
-      <c r="M20" t="str">
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -1035,7 +1035,7 @@
         <v>Anusha Badole</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1044,7 +1044,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K16" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -1076,7 +1076,7 @@
         <v>Disha Pangal</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K17" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -1158,7 +1158,7 @@
         <v>Suman Yadav</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K19" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,40 +446,40 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>PRPL/MOB/3826</v>
+        <v>PRPL/LAP/510</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D2" t="str">
-        <v>PRPL 273 SAMSUNG MOBILE</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E2" t="str">
-        <v>350284941590594</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F2" t="str">
-        <v>Returned by kanishka</v>
+        <v>Gayatri Kothavle</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>Not Yet Assigned</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>PRPL / ACQ / 08012021/ 301</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>PATNI/20-21/7983</v>
       </c>
       <c r="J2" t="str">
         <v>Working</v>
       </c>
       <c r="K2" t="str">
-        <v>Returned by kanishka / resigned</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>24-10-2026</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>08-Jan-21</v>
       </c>
     </row>
     <row r="3">
@@ -487,25 +487,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>PRPL/LAP/1476</v>
+        <v>PRPL/MOB/3826</v>
       </c>
       <c r="C3" t="str">
-        <v>Purchased Laptop</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>PRPL 415 DELL LAPTOP</v>
+        <v>PRPL 273 SAMSUNG MOBILE</v>
       </c>
       <c r="E3" t="str">
-        <v>DK85RQ2</v>
+        <v>350284941590594</v>
       </c>
       <c r="F3" t="str">
-        <v>Returned by Kanishka</v>
+        <v>Returned by kanishka</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>PRPL / ACQ / 06042023 / 00216</v>
+        <v/>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,7 +517,7 @@
         <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L3" t="str">
-        <v>24-10-26</v>
+        <v>24-10-2026</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -528,25 +528,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>1</v>
+        <v>PRPL/LAP/1476</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D4" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 415 DELL LAPTOP</v>
       </c>
       <c r="E4" t="str">
-        <v>PF3Y9355</v>
+        <v>DK85RQ2</v>
       </c>
       <c r="F4" t="str">
-        <v>Ajinkya</v>
+        <v>Returned by Kanishka</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>PRPL / ACQ / 06042023 / 00216</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -555,10 +555,10 @@
         <v>Working</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L4" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -569,7 +569,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -578,10 +578,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E5" t="str">
-        <v>PF3Z9PCW</v>
+        <v>PF3Y9355</v>
       </c>
       <c r="F5" t="str">
-        <v>Kavita</v>
+        <v>Ajinkya</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -610,19 +610,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="str">
-        <v>Mobile</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>M17 5g</v>
+        <v>Lenovo</v>
       </c>
       <c r="E6" t="str">
-        <v>355242460501645</v>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F6" t="str">
-        <v>Pradnya</v>
+        <v>Kavita</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -640,7 +640,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>With cable</v>
+        <v>#N/A</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -651,19 +651,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D7" t="str">
-        <v>HP</v>
+        <v>M17 5g</v>
       </c>
       <c r="E7" t="str">
-        <v>5CG1223Y8W</v>
+        <v>355242460501645</v>
       </c>
       <c r="F7" t="str">
-        <v>Rachna Solanki</v>
+        <v>Pradnya</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -681,7 +681,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>Dell</v>
+        <v>HP</v>
       </c>
       <c r="E8" t="str">
-        <v>J9LDVF2</v>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F8" t="str">
-        <v>Aarju Wasnik</v>
+        <v>Rachna Solanki</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -733,19 +733,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>HP</v>
+        <v>Dell</v>
       </c>
       <c r="E9" t="str">
-        <v>5CG10294SF</v>
+        <v>J9LDVF2</v>
       </c>
       <c r="F9" t="str">
-        <v>Himanshu Tayde</v>
+        <v>Aarju Wasnik</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -774,19 +774,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>Temp Laptop</v>
+        <v>HP</v>
       </c>
       <c r="E10" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG10294SF</v>
       </c>
       <c r="F10" t="str">
-        <v xml:space="preserve">Preshita </v>
+        <v>Himanshu Tayde</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -815,19 +815,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>Lenovo</v>
+        <v>Temp Laptop</v>
       </c>
       <c r="E11" t="str">
-        <v>-</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F11" t="str">
-        <v>Jivika</v>
+        <v xml:space="preserve">Preshita </v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -865,10 +865,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E12" t="str">
-        <v>PF37ZPG5</v>
+        <v>-</v>
       </c>
       <c r="F12" t="str">
-        <v>Swapnali Patekar</v>
+        <v>Jivika</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -897,19 +897,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E13" t="str">
-        <v>HQRYDB3</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F13" t="str">
-        <v>Abhishek mishra</v>
+        <v>Swapnali Patekar</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -938,7 +938,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -947,10 +947,10 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>PF37ZPG5</v>
+        <v>HQRYDB3</v>
       </c>
       <c r="F14" t="str">
-        <v>Sunny Ansul</v>
+        <v>Abhishek mishra</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -979,19 +979,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>PRPL 14 HP LAPTOP</v>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <v>5CG0346B2F</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F15" t="str">
-        <v>Palak Annawadiya</v>
+        <v>Sunny Ansul</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1020,22 +1020,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>PRPL 265 HP LAPTOP</v>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E16" t="str">
-        <v>5CG1223Y45</v>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F16" t="str">
-        <v>Anusha Badole</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G16" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1044,7 +1044,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1061,19 +1061,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E17" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F17" t="str">
-        <v>Disha Pangal</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="G17" t="str">
         <v>Returned</v>
@@ -1102,22 +1102,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E18" t="str">
-        <v>PF37KGPZ</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F18" t="str">
-        <v>Sakshi Ghorpade</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1143,22 +1143,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>Lenovo</v>
       </c>
       <c r="E19" t="str">
-        <v>5CG1223Y30</v>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F19" t="str">
-        <v>Suman Yadav</v>
+        <v>Sakshi Ghorpade</v>
       </c>
       <c r="G19" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1184,22 +1184,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>PRPL 293 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E20" t="str">
-        <v>5CG1223Y8W</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F20" t="str">
-        <v>Preshita Damahe</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1208,7 +1208,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1225,45 +1225,86 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
+        <v>17</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>PRPL 293 HP LAPTOP</v>
+      </c>
+      <c r="E21" t="str">
+        <v>5CG1223Y8W</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Preshita Damahe</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
         <v>18</v>
       </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
         <v>Lenovo</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E22" t="str">
         <v>PF3P6ZDE</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F22" t="str">
         <v>Aman singh</v>
       </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v>Working</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v>#N/A</v>
-      </c>
-      <c r="M21" t="str">
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M22" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,28 +446,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>PRPL/LAP/510</v>
+        <v>PRPL/LAP/1005</v>
       </c>
       <c r="C2" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D2" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E2" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F2" t="str">
-        <v>Gayatri Kothavle</v>
+        <v>Gauri Satsukar</v>
       </c>
       <c r="G2" t="str">
         <v>Not Yet Assigned</v>
       </c>
       <c r="H2" t="str">
-        <v>PRPL / ACQ / 08012021/ 301</v>
+        <v>PRPL / ACQ / 20122021 / 0062</v>
       </c>
       <c r="I2" t="str">
-        <v>PATNI/20-21/7983</v>
+        <v>TS/21-22/0598</v>
       </c>
       <c r="J2" t="str">
         <v>Working</v>
@@ -476,10 +476,10 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>Battery Replaced/Battery issue</v>
       </c>
       <c r="M2" t="str">
-        <v>08-Jan-21</v>
+        <v>20-Dec-21</v>
       </c>
     </row>
     <row r="3">
@@ -487,40 +487,40 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>PRPL/MOB/3826</v>
+        <v>PRPL/LAP/510</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D3" t="str">
-        <v>PRPL 273 SAMSUNG MOBILE</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E3" t="str">
-        <v>350284941590594</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F3" t="str">
-        <v>Returned by kanishka</v>
+        <v>Gayatri Kothavle</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>Not Yet Assigned</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>PRPL / ACQ / 08012021/ 301</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>PATNI/20-21/7983</v>
       </c>
       <c r="J3" t="str">
         <v>Working</v>
       </c>
       <c r="K3" t="str">
-        <v>Returned by kanishka / resigned</v>
+        <v/>
       </c>
       <c r="L3" t="str">
-        <v>24-10-2026</v>
+        <v>#N/A</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>08-Jan-21</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>PRPL/LAP/1476</v>
+        <v>PRPL/MOB/3826</v>
       </c>
       <c r="C4" t="str">
-        <v>Purchased Laptop</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>PRPL 415 DELL LAPTOP</v>
+        <v>PRPL 273 SAMSUNG MOBILE</v>
       </c>
       <c r="E4" t="str">
-        <v>DK85RQ2</v>
+        <v>350284941590594</v>
       </c>
       <c r="F4" t="str">
-        <v>Returned by Kanishka</v>
+        <v>Returned by kanishka</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>PRPL / ACQ / 06042023 / 00216</v>
+        <v/>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -558,7 +558,7 @@
         <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L4" t="str">
-        <v>24-10-26</v>
+        <v>24-10-2026</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -569,25 +569,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>1</v>
+        <v>PRPL/LAP/1476</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D5" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 415 DELL LAPTOP</v>
       </c>
       <c r="E5" t="str">
-        <v>PF3Y9355</v>
+        <v>DK85RQ2</v>
       </c>
       <c r="F5" t="str">
-        <v>Ajinkya</v>
+        <v>Returned by Kanishka</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>PRPL / ACQ / 06042023 / 00216</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -596,10 +596,10 @@
         <v>Working</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L5" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -610,7 +610,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -619,10 +619,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E6" t="str">
-        <v>PF3Z9PCW</v>
+        <v>PF3Y9355</v>
       </c>
       <c r="F6" t="str">
-        <v>Kavita</v>
+        <v>Ajinkya</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -651,19 +651,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>Mobile</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>M17 5g</v>
+        <v>Lenovo</v>
       </c>
       <c r="E7" t="str">
-        <v>355242460501645</v>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F7" t="str">
-        <v>Pradnya</v>
+        <v>Kavita</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -681,7 +681,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>With cable</v>
+        <v>#N/A</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D8" t="str">
-        <v>HP</v>
+        <v>M17 5g</v>
       </c>
       <c r="E8" t="str">
-        <v>5CG1223Y8W</v>
+        <v>355242460501645</v>
       </c>
       <c r="F8" t="str">
-        <v>Rachna Solanki</v>
+        <v>Pradnya</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -733,19 +733,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>Dell</v>
+        <v>HP</v>
       </c>
       <c r="E9" t="str">
-        <v>J9LDVF2</v>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F9" t="str">
-        <v>Aarju Wasnik</v>
+        <v>Rachna Solanki</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -774,19 +774,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>HP</v>
+        <v>Dell</v>
       </c>
       <c r="E10" t="str">
-        <v>5CG10294SF</v>
+        <v>J9LDVF2</v>
       </c>
       <c r="F10" t="str">
-        <v>Himanshu Tayde</v>
+        <v>Aarju Wasnik</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -815,19 +815,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>Temp Laptop</v>
+        <v>HP</v>
       </c>
       <c r="E11" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG10294SF</v>
       </c>
       <c r="F11" t="str">
-        <v xml:space="preserve">Preshita </v>
+        <v>Himanshu Tayde</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -856,19 +856,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>Lenovo</v>
+        <v>Temp Laptop</v>
       </c>
       <c r="E12" t="str">
-        <v>-</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F12" t="str">
-        <v>Jivika</v>
+        <v xml:space="preserve">Preshita </v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -897,7 +897,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -906,10 +906,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E13" t="str">
-        <v>PF37ZPG5</v>
+        <v>-</v>
       </c>
       <c r="F13" t="str">
-        <v>Swapnali Patekar</v>
+        <v>Jivika</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -938,19 +938,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E14" t="str">
-        <v>HQRYDB3</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F14" t="str">
-        <v>Abhishek mishra</v>
+        <v>Swapnali Patekar</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -979,7 +979,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -988,10 +988,10 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>PF37ZPG5</v>
+        <v>HQRYDB3</v>
       </c>
       <c r="F15" t="str">
-        <v>Sunny Ansul</v>
+        <v>Abhishek mishra</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1020,19 +1020,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>PRPL 14 HP LAPTOP</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>5CG0346B2F</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F16" t="str">
-        <v>Palak Annawadiya</v>
+        <v>Sunny Ansul</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1061,22 +1061,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>PRPL 265 HP LAPTOP</v>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E17" t="str">
-        <v>5CG1223Y45</v>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F17" t="str">
-        <v>Anusha Badole</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G17" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1102,19 +1102,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E18" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F18" t="str">
-        <v>Disha Pangal</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="G18" t="str">
         <v>Returned</v>
@@ -1143,22 +1143,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E19" t="str">
-        <v>PF37KGPZ</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F19" t="str">
-        <v>Sakshi Ghorpade</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1184,22 +1184,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>Lenovo</v>
       </c>
       <c r="E20" t="str">
-        <v>5CG1223Y30</v>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F20" t="str">
-        <v>Suman Yadav</v>
+        <v>Sakshi Ghorpade</v>
       </c>
       <c r="G20" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1208,7 +1208,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1225,22 +1225,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>PRPL 293 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E21" t="str">
-        <v>5CG1223Y8W</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F21" t="str">
-        <v>Preshita Damahe</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1266,45 +1266,86 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
+        <v>17</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>PRPL 293 HP LAPTOP</v>
+      </c>
+      <c r="E22" t="str">
+        <v>5CG1223Y8W</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Preshita Damahe</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
         <v>18</v>
       </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
         <v>Lenovo</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E23" t="str">
         <v>PF3P6ZDE</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F23" t="str">
         <v>Aman singh</v>
       </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v>Working</v>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v>#N/A</v>
-      </c>
-      <c r="M22" t="str">
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M23" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,40 +446,40 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>PRPL/LAP/1005</v>
+        <v>PRPL/LAP/543</v>
       </c>
       <c r="C2" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D2" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>PRPL 231 HP LAPTOP</v>
       </c>
       <c r="E2" t="str">
-        <v>5CG1223Y30</v>
+        <v>DK85R02</v>
       </c>
       <c r="F2" t="str">
-        <v>Gauri Satsukar</v>
+        <v>Neha Singh</v>
       </c>
       <c r="G2" t="str">
-        <v>Not Yet Assigned</v>
+        <v>Available</v>
       </c>
       <c r="H2" t="str">
-        <v>PRPL / ACQ / 20122021 / 0062</v>
+        <v>ACQ/LAP/001</v>
       </c>
       <c r="I2" t="str">
-        <v>TS/21-22/0598</v>
+        <v>PATNI/20-21/8688</v>
       </c>
       <c r="J2" t="str">
-        <v>Working</v>
+        <v>Replaced</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>Replaced by Dell: 5CG102928W</v>
       </c>
       <c r="L2" t="str">
-        <v>Battery Replaced/Battery issue</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>20-Dec-21</v>
+        <v>28 oct 2026</v>
       </c>
     </row>
     <row r="3">
@@ -487,28 +487,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>PRPL/LAP/510</v>
+        <v>PRPL/LAP/1005</v>
       </c>
       <c r="C3" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D3" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E3" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F3" t="str">
-        <v>Gayatri Kothavle</v>
+        <v>Gauri Satsukar</v>
       </c>
       <c r="G3" t="str">
         <v>Not Yet Assigned</v>
       </c>
       <c r="H3" t="str">
-        <v>PRPL / ACQ / 08012021/ 301</v>
+        <v>PRPL / ACQ / 20122021 / 0062</v>
       </c>
       <c r="I3" t="str">
-        <v>PATNI/20-21/7983</v>
+        <v>TS/21-22/0598</v>
       </c>
       <c r="J3" t="str">
         <v>Working</v>
@@ -517,10 +517,10 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>#N/A</v>
+        <v>Battery Replaced/Battery issue</v>
       </c>
       <c r="M3" t="str">
-        <v>08-Jan-21</v>
+        <v>20-Dec-21</v>
       </c>
     </row>
     <row r="4">
@@ -528,40 +528,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>PRPL/MOB/3826</v>
+        <v>PRPL/LAP/510</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D4" t="str">
-        <v>PRPL 273 SAMSUNG MOBILE</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E4" t="str">
-        <v>350284941590594</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F4" t="str">
-        <v>Returned by kanishka</v>
+        <v>Gayatri Kothavle</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>Not Yet Assigned</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>PRPL / ACQ / 08012021/ 301</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>PATNI/20-21/7983</v>
       </c>
       <c r="J4" t="str">
         <v>Working</v>
       </c>
       <c r="K4" t="str">
-        <v>Returned by kanishka / resigned</v>
+        <v/>
       </c>
       <c r="L4" t="str">
-        <v>24-10-2026</v>
+        <v>#N/A</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>08-Jan-21</v>
       </c>
     </row>
     <row r="5">
@@ -569,25 +569,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>PRPL/LAP/1476</v>
+        <v>PRPL/MOB/3826</v>
       </c>
       <c r="C5" t="str">
-        <v>Purchased Laptop</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>PRPL 415 DELL LAPTOP</v>
+        <v>PRPL 273 SAMSUNG MOBILE</v>
       </c>
       <c r="E5" t="str">
-        <v>DK85RQ2</v>
+        <v>350284941590594</v>
       </c>
       <c r="F5" t="str">
-        <v>Returned by Kanishka</v>
+        <v>Returned by kanishka</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>PRPL / ACQ / 06042023 / 00216</v>
+        <v/>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -599,7 +599,7 @@
         <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L5" t="str">
-        <v>24-10-26</v>
+        <v>24-10-2026</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -610,25 +610,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>1</v>
+        <v>PRPL/LAP/1476</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D6" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 415 DELL LAPTOP</v>
       </c>
       <c r="E6" t="str">
-        <v>PF3Y9355</v>
+        <v>DK85RQ2</v>
       </c>
       <c r="F6" t="str">
-        <v>Ajinkya</v>
+        <v>Returned by Kanishka</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>PRPL / ACQ / 06042023 / 00216</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -637,10 +637,10 @@
         <v>Working</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L6" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -651,7 +651,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -660,10 +660,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E7" t="str">
-        <v>PF3Z9PCW</v>
+        <v>PF3Y9355</v>
       </c>
       <c r="F7" t="str">
-        <v>Kavita</v>
+        <v>Ajinkya</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -692,19 +692,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>Mobile</v>
+        <v/>
       </c>
       <c r="D8" t="str">
-        <v>M17 5g</v>
+        <v>Lenovo</v>
       </c>
       <c r="E8" t="str">
-        <v>355242460501645</v>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F8" t="str">
-        <v>Pradnya</v>
+        <v>Kavita</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>With cable</v>
+        <v>#N/A</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -733,19 +733,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D9" t="str">
-        <v>HP</v>
+        <v>M17 5g</v>
       </c>
       <c r="E9" t="str">
-        <v>5CG1223Y8W</v>
+        <v>355242460501645</v>
       </c>
       <c r="F9" t="str">
-        <v>Rachna Solanki</v>
+        <v>Pradnya</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -763,7 +763,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -774,19 +774,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>Dell</v>
+        <v>HP</v>
       </c>
       <c r="E10" t="str">
-        <v>J9LDVF2</v>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F10" t="str">
-        <v>Aarju Wasnik</v>
+        <v>Rachna Solanki</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -815,19 +815,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>HP</v>
+        <v>Dell</v>
       </c>
       <c r="E11" t="str">
-        <v>5CG10294SF</v>
+        <v>J9LDVF2</v>
       </c>
       <c r="F11" t="str">
-        <v>Himanshu Tayde</v>
+        <v>Aarju Wasnik</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -856,19 +856,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>Temp Laptop</v>
+        <v>HP</v>
       </c>
       <c r="E12" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG10294SF</v>
       </c>
       <c r="F12" t="str">
-        <v xml:space="preserve">Preshita </v>
+        <v>Himanshu Tayde</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -897,19 +897,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>Lenovo</v>
+        <v>Temp Laptop</v>
       </c>
       <c r="E13" t="str">
-        <v>-</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F13" t="str">
-        <v>Jivika</v>
+        <v xml:space="preserve">Preshita </v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -938,7 +938,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -947,10 +947,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E14" t="str">
-        <v>PF37ZPG5</v>
+        <v>-</v>
       </c>
       <c r="F14" t="str">
-        <v>Swapnali Patekar</v>
+        <v>Jivika</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -979,19 +979,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E15" t="str">
-        <v>HQRYDB3</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F15" t="str">
-        <v>Abhishek mishra</v>
+        <v>Swapnali Patekar</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1020,7 +1020,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -1029,10 +1029,10 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>PF37ZPG5</v>
+        <v>HQRYDB3</v>
       </c>
       <c r="F16" t="str">
-        <v>Sunny Ansul</v>
+        <v>Abhishek mishra</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1061,19 +1061,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>PRPL 14 HP LAPTOP</v>
+        <v/>
       </c>
       <c r="E17" t="str">
-        <v>5CG0346B2F</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F17" t="str">
-        <v>Palak Annawadiya</v>
+        <v>Sunny Ansul</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1102,22 +1102,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>PRPL 265 HP LAPTOP</v>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E18" t="str">
-        <v>5CG1223Y45</v>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F18" t="str">
-        <v>Anusha Badole</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G18" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1143,19 +1143,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E19" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F19" t="str">
-        <v>Disha Pangal</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="G19" t="str">
         <v>Returned</v>
@@ -1184,22 +1184,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E20" t="str">
-        <v>PF37KGPZ</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F20" t="str">
-        <v>Sakshi Ghorpade</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1208,7 +1208,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1225,22 +1225,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>Lenovo</v>
       </c>
       <c r="E21" t="str">
-        <v>5CG1223Y30</v>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F21" t="str">
-        <v>Suman Yadav</v>
+        <v>Sakshi Ghorpade</v>
       </c>
       <c r="G21" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1266,22 +1266,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>PRPL 293 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E22" t="str">
-        <v>5CG1223Y8W</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F22" t="str">
-        <v>Preshita Damahe</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1290,7 +1290,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -1307,45 +1307,86 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
+        <v>17</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>PRPL 293 HP LAPTOP</v>
+      </c>
+      <c r="E23" t="str">
+        <v>5CG1223Y8W</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Preshita Damahe</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
         <v>18</v>
       </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
         <v>Lenovo</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E24" t="str">
         <v>PF3P6ZDE</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F24" t="str">
         <v>Aman singh</v>
       </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v>Working</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v>#N/A</v>
-      </c>
-      <c r="M23" t="str">
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M24" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -476,7 +476,7 @@
         <v>Replaced by Dell: 5CG102928W</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>#N/A</v>
       </c>
       <c r="M2" t="str">
         <v>28 oct 2026</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K23" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -1322,7 +1322,7 @@
         <v>Preshita Damahe</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H23" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -1161,7 +1161,7 @@
         <v>Returned</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Temp for VC</v>
       </c>
       <c r="I19" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,40 +446,40 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>PRPL/LAP/543</v>
+        <v>PRPL/LAP/889</v>
       </c>
       <c r="C2" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D2" t="str">
-        <v>PRPL 231 HP LAPTOP</v>
+        <v>PRPL 264 HP LAPTOP</v>
       </c>
       <c r="E2" t="str">
-        <v>DK85R02</v>
+        <v>5CG1224130</v>
       </c>
       <c r="F2" t="str">
-        <v>Neha Singh</v>
+        <v>Mayuresh</v>
       </c>
       <c r="G2" t="str">
-        <v>Available</v>
+        <v>Temp for Editing</v>
       </c>
       <c r="H2" t="str">
-        <v>ACQ/LAP/001</v>
+        <v>PRPL / ACQ / 16082021 / 0033</v>
       </c>
       <c r="I2" t="str">
-        <v>PATNI/20-21/8688</v>
+        <v>PATNI21-22/10467</v>
       </c>
       <c r="J2" t="str">
-        <v>Replaced</v>
+        <v>Working</v>
       </c>
       <c r="K2" t="str">
-        <v>Replaced by Dell: 5CG102928W</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>28 oct 2026</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -487,40 +487,40 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>PRPL/LAP/1005</v>
+        <v>PRPL/LAP/543</v>
       </c>
       <c r="C3" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D3" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>PRPL 231 HP LAPTOP</v>
       </c>
       <c r="E3" t="str">
-        <v>5CG1223Y30</v>
+        <v>DK85R02</v>
       </c>
       <c r="F3" t="str">
-        <v>Gauri Satsukar</v>
+        <v>Neha Singh</v>
       </c>
       <c r="G3" t="str">
-        <v>Not Yet Assigned</v>
+        <v>Available</v>
       </c>
       <c r="H3" t="str">
-        <v>PRPL / ACQ / 20122021 / 0062</v>
+        <v>ACQ/LAP/001</v>
       </c>
       <c r="I3" t="str">
-        <v>TS/21-22/0598</v>
+        <v>PATNI/20-21/8688</v>
       </c>
       <c r="J3" t="str">
-        <v>Working</v>
+        <v>Replaced</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>Replaced by Dell: 5CG102928W</v>
       </c>
       <c r="L3" t="str">
-        <v>Battery Replaced/Battery issue</v>
+        <v>#N/A</v>
       </c>
       <c r="M3" t="str">
-        <v>20-Dec-21</v>
+        <v>28 oct 2026</v>
       </c>
     </row>
     <row r="4">
@@ -528,28 +528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>PRPL/LAP/510</v>
+        <v>PRPL/LAP/1005</v>
       </c>
       <c r="C4" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D4" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E4" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F4" t="str">
-        <v>Gayatri Kothavle</v>
+        <v>Gauri Satsukar</v>
       </c>
       <c r="G4" t="str">
         <v>Not Yet Assigned</v>
       </c>
       <c r="H4" t="str">
-        <v>PRPL / ACQ / 08012021/ 301</v>
+        <v>PRPL / ACQ / 20122021 / 0062</v>
       </c>
       <c r="I4" t="str">
-        <v>PATNI/20-21/7983</v>
+        <v>TS/21-22/0598</v>
       </c>
       <c r="J4" t="str">
         <v>Working</v>
@@ -558,10 +558,10 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>#N/A</v>
+        <v>Battery Replaced/Battery issue</v>
       </c>
       <c r="M4" t="str">
-        <v>08-Jan-21</v>
+        <v>20-Dec-21</v>
       </c>
     </row>
     <row r="5">
@@ -569,40 +569,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>PRPL/MOB/3826</v>
+        <v>PRPL/LAP/510</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D5" t="str">
-        <v>PRPL 273 SAMSUNG MOBILE</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E5" t="str">
-        <v>350284941590594</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F5" t="str">
-        <v>Returned by kanishka</v>
+        <v>Gayatri Kothavle</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>Not Yet Assigned</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>PRPL / ACQ / 08012021/ 301</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>PATNI/20-21/7983</v>
       </c>
       <c r="J5" t="str">
         <v>Working</v>
       </c>
       <c r="K5" t="str">
-        <v>Returned by kanishka / resigned</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>24-10-2026</v>
+        <v>#N/A</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>08-Jan-21</v>
       </c>
     </row>
     <row r="6">
@@ -610,25 +610,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>PRPL/LAP/1476</v>
+        <v>PRPL/MOB/3826</v>
       </c>
       <c r="C6" t="str">
-        <v>Purchased Laptop</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>PRPL 415 DELL LAPTOP</v>
+        <v>PRPL 273 SAMSUNG MOBILE</v>
       </c>
       <c r="E6" t="str">
-        <v>DK85RQ2</v>
+        <v>350284941590594</v>
       </c>
       <c r="F6" t="str">
-        <v>Returned by Kanishka</v>
+        <v>Returned by kanishka</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>PRPL / ACQ / 06042023 / 00216</v>
+        <v/>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -640,7 +640,7 @@
         <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L6" t="str">
-        <v>24-10-26</v>
+        <v>24-10-2026</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -651,25 +651,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>1</v>
+        <v>PRPL/LAP/1476</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D7" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 415 DELL LAPTOP</v>
       </c>
       <c r="E7" t="str">
-        <v>PF3Y9355</v>
+        <v>DK85RQ2</v>
       </c>
       <c r="F7" t="str">
-        <v>Ajinkya</v>
+        <v>Returned by Kanishka</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>PRPL / ACQ / 06042023 / 00216</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -678,10 +678,10 @@
         <v>Working</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L7" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -692,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -701,10 +701,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E8" t="str">
-        <v>PF3Z9PCW</v>
+        <v>PF3Y9355</v>
       </c>
       <c r="F8" t="str">
-        <v>Kavita</v>
+        <v>Ajinkya</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -733,19 +733,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="str">
-        <v>Mobile</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>M17 5g</v>
+        <v>Lenovo</v>
       </c>
       <c r="E9" t="str">
-        <v>355242460501645</v>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F9" t="str">
-        <v>Pradnya</v>
+        <v>Kavita</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -763,7 +763,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>With cable</v>
+        <v>#N/A</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -774,19 +774,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D10" t="str">
-        <v>HP</v>
+        <v>M17 5g</v>
       </c>
       <c r="E10" t="str">
-        <v>5CG1223Y8W</v>
+        <v>355242460501645</v>
       </c>
       <c r="F10" t="str">
-        <v>Rachna Solanki</v>
+        <v>Pradnya</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -815,19 +815,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>Dell</v>
+        <v>HP</v>
       </c>
       <c r="E11" t="str">
-        <v>J9LDVF2</v>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F11" t="str">
-        <v>Aarju Wasnik</v>
+        <v>Rachna Solanki</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -856,19 +856,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>HP</v>
+        <v>Dell</v>
       </c>
       <c r="E12" t="str">
-        <v>5CG10294SF</v>
+        <v>J9LDVF2</v>
       </c>
       <c r="F12" t="str">
-        <v>Himanshu Tayde</v>
+        <v>Aarju Wasnik</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -897,19 +897,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>Temp Laptop</v>
+        <v>HP</v>
       </c>
       <c r="E13" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG10294SF</v>
       </c>
       <c r="F13" t="str">
-        <v xml:space="preserve">Preshita </v>
+        <v>Himanshu Tayde</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -938,19 +938,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>Lenovo</v>
+        <v>Temp Laptop</v>
       </c>
       <c r="E14" t="str">
-        <v>-</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F14" t="str">
-        <v>Jivika</v>
+        <v xml:space="preserve">Preshita </v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -979,7 +979,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -988,10 +988,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E15" t="str">
-        <v>PF37ZPG5</v>
+        <v>-</v>
       </c>
       <c r="F15" t="str">
-        <v>Swapnali Patekar</v>
+        <v>Jivika</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1020,19 +1020,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E16" t="str">
-        <v>HQRYDB3</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F16" t="str">
-        <v>Abhishek mishra</v>
+        <v>Swapnali Patekar</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1061,7 +1061,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -1070,10 +1070,10 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>PF37ZPG5</v>
+        <v>HQRYDB3</v>
       </c>
       <c r="F17" t="str">
-        <v>Sunny Ansul</v>
+        <v>Abhishek mishra</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1102,19 +1102,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>PRPL 14 HP LAPTOP</v>
+        <v/>
       </c>
       <c r="E18" t="str">
-        <v>5CG0346B2F</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F18" t="str">
-        <v>Palak Annawadiya</v>
+        <v>Sunny Ansul</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1143,31 +1143,31 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>PRPL 265 HP LAPTOP</v>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E19" t="str">
-        <v>5CG1223Y45</v>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F19" t="str">
-        <v>Anusha Badole</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G19" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>Temp for VC</v>
+        <v/>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1184,25 +1184,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E20" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F20" t="str">
-        <v>Disha Pangal</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="G20" t="str">
         <v>Returned</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Temp for VC</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1225,22 +1225,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E21" t="str">
-        <v>PF37KGPZ</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F21" t="str">
-        <v>Sakshi Ghorpade</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1266,22 +1266,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>Lenovo</v>
       </c>
       <c r="E22" t="str">
-        <v>5CG1223Y30</v>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F22" t="str">
-        <v>Suman Yadav</v>
+        <v>Sakshi Ghorpade</v>
       </c>
       <c r="G22" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1290,7 +1290,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -1307,19 +1307,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>PRPL 293 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E23" t="str">
-        <v>5CG1223Y8W</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F23" t="str">
-        <v>Preshita Damahe</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G23" t="str">
         <v>Returned</v>
@@ -1348,45 +1348,86 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
+        <v>17</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>PRPL 293 HP LAPTOP</v>
+      </c>
+      <c r="E24" t="str">
+        <v>5CG1223Y8W</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Preshita Damahe</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Returned</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>Available</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
         <v>18</v>
       </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
         <v>Lenovo</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E25" t="str">
         <v>PF3P6ZDE</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F25" t="str">
         <v>Aman singh</v>
       </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v>Working</v>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v>#N/A</v>
-      </c>
-      <c r="M24" t="str">
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M25" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -476,7 +476,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>#N/A</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -1208,7 +1208,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K20" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -1196,19 +1196,19 @@
         <v>5CG1223Y45</v>
       </c>
       <c r="F20" t="str">
-        <v>Anusha Badole</v>
+        <v>Stock in Turbhe office</v>
       </c>
       <c r="G20" t="str">
         <v>Returned</v>
       </c>
       <c r="H20" t="str">
-        <v>Temp for VC</v>
+        <v/>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K20" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,28 +446,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>PRPL/LAP/889</v>
+        <v>Extention Board</v>
       </c>
       <c r="C2" t="str">
-        <v>Purchased Laptop</v>
+        <v>Extention Board</v>
       </c>
       <c r="D2" t="str">
-        <v>PRPL 264 HP LAPTOP</v>
+        <v>Extention Board</v>
       </c>
       <c r="E2" t="str">
-        <v>5CG1224130</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>Mayuresh</v>
+        <v>To Office Boys</v>
       </c>
       <c r="G2" t="str">
-        <v>Temp for Editing</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>PRPL / ACQ / 16082021 / 0033</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>PATNI21-22/10467</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>Working</v>
@@ -476,10 +476,10 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>#N/A</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>31-10-26</v>
       </c>
     </row>
     <row r="3">
@@ -487,40 +487,40 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>PRPL/LAP/543</v>
+        <v>PRPL/LAP/889</v>
       </c>
       <c r="C3" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D3" t="str">
-        <v>PRPL 231 HP LAPTOP</v>
+        <v>PRPL 264 HP LAPTOP</v>
       </c>
       <c r="E3" t="str">
-        <v>DK85R02</v>
+        <v>5CG1224130</v>
       </c>
       <c r="F3" t="str">
-        <v>Neha Singh</v>
+        <v>Mayuresh</v>
       </c>
       <c r="G3" t="str">
-        <v>Available</v>
+        <v>Temp for Editing</v>
       </c>
       <c r="H3" t="str">
-        <v>ACQ/LAP/001</v>
+        <v>PRPL / ACQ / 16082021 / 0033</v>
       </c>
       <c r="I3" t="str">
-        <v>PATNI/20-21/8688</v>
+        <v>PATNI21-22/10467</v>
       </c>
       <c r="J3" t="str">
-        <v>Replaced</v>
+        <v>Working</v>
       </c>
       <c r="K3" t="str">
-        <v>Replaced by Dell: 5CG102928W</v>
+        <v/>
       </c>
       <c r="L3" t="str">
         <v>#N/A</v>
       </c>
       <c r="M3" t="str">
-        <v>28 oct 2026</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -528,40 +528,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>PRPL/LAP/1005</v>
+        <v>PRPL/LAP/543</v>
       </c>
       <c r="C4" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D4" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>PRPL 231 HP LAPTOP</v>
       </c>
       <c r="E4" t="str">
-        <v>5CG1223Y30</v>
+        <v>DK85R02</v>
       </c>
       <c r="F4" t="str">
-        <v>Gauri Satsukar</v>
+        <v>Neha Singh</v>
       </c>
       <c r="G4" t="str">
-        <v>Not Yet Assigned</v>
+        <v>Available</v>
       </c>
       <c r="H4" t="str">
-        <v>PRPL / ACQ / 20122021 / 0062</v>
+        <v>ACQ/LAP/001</v>
       </c>
       <c r="I4" t="str">
-        <v>TS/21-22/0598</v>
+        <v>PATNI/20-21/8688</v>
       </c>
       <c r="J4" t="str">
-        <v>Working</v>
+        <v>Replaced</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>Replaced by Dell: 5CG102928W</v>
       </c>
       <c r="L4" t="str">
-        <v>Battery Replaced/Battery issue</v>
+        <v>#N/A</v>
       </c>
       <c r="M4" t="str">
-        <v>20-Dec-21</v>
+        <v>28 oct 2026</v>
       </c>
     </row>
     <row r="5">
@@ -569,28 +569,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>PRPL/LAP/510</v>
+        <v>PRPL/LAP/1005</v>
       </c>
       <c r="C5" t="str">
         <v>Purchased Laptop</v>
       </c>
       <c r="D5" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E5" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F5" t="str">
-        <v>Gayatri Kothavle</v>
+        <v>Gauri Satsukar</v>
       </c>
       <c r="G5" t="str">
         <v>Not Yet Assigned</v>
       </c>
       <c r="H5" t="str">
-        <v>PRPL / ACQ / 08012021/ 301</v>
+        <v>PRPL / ACQ / 20122021 / 0062</v>
       </c>
       <c r="I5" t="str">
-        <v>PATNI/20-21/7983</v>
+        <v>TS/21-22/0598</v>
       </c>
       <c r="J5" t="str">
         <v>Working</v>
@@ -599,10 +599,10 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>#N/A</v>
+        <v>Battery Replaced/Battery issue</v>
       </c>
       <c r="M5" t="str">
-        <v>08-Jan-21</v>
+        <v>20-Dec-21</v>
       </c>
     </row>
     <row r="6">
@@ -610,40 +610,40 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>PRPL/MOB/3826</v>
+        <v>PRPL/LAP/510</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D6" t="str">
-        <v>PRPL 273 SAMSUNG MOBILE</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E6" t="str">
-        <v>350284941590594</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F6" t="str">
-        <v>Returned by kanishka</v>
+        <v>Gayatri Kothavle</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Not Yet Assigned</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>PRPL / ACQ / 08012021/ 301</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>PATNI/20-21/7983</v>
       </c>
       <c r="J6" t="str">
         <v>Working</v>
       </c>
       <c r="K6" t="str">
-        <v>Returned by kanishka / resigned</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>24-10-2026</v>
+        <v>#N/A</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>08-Jan-21</v>
       </c>
     </row>
     <row r="7">
@@ -651,25 +651,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>PRPL/LAP/1476</v>
+        <v>PRPL/MOB/3826</v>
       </c>
       <c r="C7" t="str">
-        <v>Purchased Laptop</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>PRPL 415 DELL LAPTOP</v>
+        <v>PRPL 273 SAMSUNG MOBILE</v>
       </c>
       <c r="E7" t="str">
-        <v>DK85RQ2</v>
+        <v>350284941590594</v>
       </c>
       <c r="F7" t="str">
-        <v>Returned by Kanishka</v>
+        <v>Returned by kanishka</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>PRPL / ACQ / 06042023 / 00216</v>
+        <v/>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -681,7 +681,7 @@
         <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L7" t="str">
-        <v>24-10-26</v>
+        <v>24-10-2026</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -692,25 +692,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>1</v>
+        <v>PRPL/LAP/1476</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>Purchased Laptop</v>
       </c>
       <c r="D8" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 415 DELL LAPTOP</v>
       </c>
       <c r="E8" t="str">
-        <v>PF3Y9355</v>
+        <v>DK85RQ2</v>
       </c>
       <c r="F8" t="str">
-        <v>Ajinkya</v>
+        <v>Returned by Kanishka</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>PRPL / ACQ / 06042023 / 00216</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -719,10 +719,10 @@
         <v>Working</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L8" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -733,7 +733,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -742,10 +742,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E9" t="str">
-        <v>PF3Z9PCW</v>
+        <v>PF3Y9355</v>
       </c>
       <c r="F9" t="str">
-        <v>Kavita</v>
+        <v>Ajinkya</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -774,19 +774,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="str">
-        <v>Mobile</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>M17 5g</v>
+        <v>Lenovo</v>
       </c>
       <c r="E10" t="str">
-        <v>355242460501645</v>
+        <v>PF3Z9PCW</v>
       </c>
       <c r="F10" t="str">
-        <v>Pradnya</v>
+        <v>Kavita</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>With cable</v>
+        <v>#N/A</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -815,19 +815,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>Mobile</v>
       </c>
       <c r="D11" t="str">
-        <v>HP</v>
+        <v>M17 5g</v>
       </c>
       <c r="E11" t="str">
-        <v>5CG1223Y8W</v>
+        <v>355242460501645</v>
       </c>
       <c r="F11" t="str">
-        <v>Rachna Solanki</v>
+        <v>Pradnya</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -845,7 +845,7 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>#N/A</v>
+        <v>With cable</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -856,19 +856,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>Dell</v>
+        <v>HP</v>
       </c>
       <c r="E12" t="str">
-        <v>J9LDVF2</v>
+        <v>5CG1223Y8W</v>
       </c>
       <c r="F12" t="str">
-        <v>Aarju Wasnik</v>
+        <v>Rachna Solanki</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -897,19 +897,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>HP</v>
+        <v>Dell</v>
       </c>
       <c r="E13" t="str">
-        <v>5CG10294SF</v>
+        <v>J9LDVF2</v>
       </c>
       <c r="F13" t="str">
-        <v>Himanshu Tayde</v>
+        <v>Aarju Wasnik</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -938,19 +938,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>Temp Laptop</v>
+        <v>HP</v>
       </c>
       <c r="E14" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG10294SF</v>
       </c>
       <c r="F14" t="str">
-        <v xml:space="preserve">Preshita </v>
+        <v>Himanshu Tayde</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -979,19 +979,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>Lenovo</v>
+        <v>Temp Laptop</v>
       </c>
       <c r="E15" t="str">
-        <v>-</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F15" t="str">
-        <v>Jivika</v>
+        <v xml:space="preserve">Preshita </v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1020,7 +1020,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -1029,10 +1029,10 @@
         <v>Lenovo</v>
       </c>
       <c r="E16" t="str">
-        <v>PF37ZPG5</v>
+        <v>-</v>
       </c>
       <c r="F16" t="str">
-        <v>Swapnali Patekar</v>
+        <v>Jivika</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1061,19 +1061,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>Lenovo</v>
       </c>
       <c r="E17" t="str">
-        <v>HQRYDB3</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F17" t="str">
-        <v>Abhishek mishra</v>
+        <v>Swapnali Patekar</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1102,7 +1102,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -1111,10 +1111,10 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>PF37ZPG5</v>
+        <v>HQRYDB3</v>
       </c>
       <c r="F18" t="str">
-        <v>Sunny Ansul</v>
+        <v>Abhishek mishra</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1143,19 +1143,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>PRPL 14 HP LAPTOP</v>
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>5CG0346B2F</v>
+        <v>PF37ZPG5</v>
       </c>
       <c r="F19" t="str">
-        <v>Palak Annawadiya</v>
+        <v>Sunny Ansul</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1184,22 +1184,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>PRPL 265 HP LAPTOP</v>
+        <v>PRPL 14 HP LAPTOP</v>
       </c>
       <c r="E20" t="str">
-        <v>5CG1223Y45</v>
+        <v>5CG0346B2F</v>
       </c>
       <c r="F20" t="str">
-        <v>Stock in Turbhe office</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G20" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1208,7 +1208,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1225,19 +1225,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>PRPL 206 HP LAPTOP</v>
+        <v>PRPL 265 HP LAPTOP</v>
       </c>
       <c r="E21" t="str">
-        <v>5CG0346FQN</v>
+        <v>5CG1223Y45</v>
       </c>
       <c r="F21" t="str">
-        <v>Disha Pangal</v>
+        <v>Stock in Turbhe office</v>
       </c>
       <c r="G21" t="str">
         <v>Returned</v>
@@ -1266,22 +1266,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>Lenovo</v>
+        <v>PRPL 206 HP LAPTOP</v>
       </c>
       <c r="E22" t="str">
-        <v>PF37KGPZ</v>
+        <v>5CG0346FQN</v>
       </c>
       <c r="F22" t="str">
-        <v>Sakshi Ghorpade</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>Returned</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1290,7 +1290,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -1307,22 +1307,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>PRPL 312 HP LAPTOP</v>
+        <v>Lenovo</v>
       </c>
       <c r="E23" t="str">
-        <v>5CG1223Y30</v>
+        <v>PF37KGPZ</v>
       </c>
       <c r="F23" t="str">
-        <v>Suman Yadav</v>
+        <v>Sakshi Ghorpade</v>
       </c>
       <c r="G23" t="str">
-        <v>Returned</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>Available</v>
+        <v>Working</v>
       </c>
       <c r="K23" t="str">
         <v/>
@@ -1348,19 +1348,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>PRPL 293 HP LAPTOP</v>
+        <v>PRPL 312 HP LAPTOP</v>
       </c>
       <c r="E24" t="str">
-        <v>5CG1223Y8W</v>
+        <v>5CG1223Y30</v>
       </c>
       <c r="F24" t="str">
-        <v>Preshita Damahe</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G24" t="str">
         <v>Returned</v>
@@ -1389,45 +1389,86 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
+        <v>17</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>PRPL 293 HP LAPTOP</v>
+      </c>
+      <c r="E25" t="str">
+        <v>5CG1223Y8W</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Preshita Damahe</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Returned</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>Available</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
         <v>18</v>
       </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
         <v>Lenovo</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E26" t="str">
         <v>PF3P6ZDE</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F26" t="str">
         <v>Aman singh</v>
       </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v>Working</v>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" t="str">
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>Working</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M26"/>
   </ignoredErrors>
 </worksheet>
 </file>